--- a/doc/_static/example-files/PMHC-4-1-treatment.xlsx
+++ b/doc/_static/example-files/PMHC-4-1-treatment.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennib/Work/git/PMHC/spec/doc/_static/example-files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AB6949-DE3F-9A43-BFDC-AE132C3EEA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -20,7 +26,7 @@
     <sheet name="Service Contact Practitioners" sheetId="11" r:id="rId11"/>
     <sheet name="Practitioners" sheetId="12" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -981,8 +987,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1019,13 +1025,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1063,7 +1077,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1097,6 +1111,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1131,9 +1146,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1306,11 +1322,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1318,7 +1334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1326,12 +1342,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -1340,11 +1356,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1403,7 +1419,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1459,7 +1475,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1515,7 +1531,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1571,7 +1587,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1627,7 +1643,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1683,7 +1699,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1739,7 +1755,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1795,7 +1811,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1851,7 +1867,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1907,7 +1923,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1969,11 +1985,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1990,7 +2006,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2007,7 +2023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2024,7 +2040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2041,7 +2057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2058,7 +2074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2075,7 +2091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2092,7 +2108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2109,7 +2125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2126,7 +2142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2143,7 +2159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2160,7 +2176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2177,7 +2193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -2200,11 +2216,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2233,7 +2249,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2259,7 +2275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2285,7 +2301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2311,7 +2327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2337,7 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2363,7 +2379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2389,7 +2405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2415,7 +2431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2441,7 +2457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2467,7 +2483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2499,11 +2515,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2538,7 +2554,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2567,7 +2583,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2599,11 +2615,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2638,7 +2654,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2670,7 +2686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2702,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2734,7 +2750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2766,7 +2782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2804,11 +2820,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AD11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2900,7 +2916,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2989,7 +3005,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3081,7 +3097,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3170,7 +3186,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3259,7 +3275,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3348,7 +3364,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3434,7 +3450,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3523,7 +3539,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3612,7 +3628,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -3701,7 +3717,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3793,11 +3809,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>92</v>
       </c>
@@ -3811,7 +3827,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3825,7 +3841,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3839,7 +3855,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3853,7 +3869,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3867,7 +3883,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3881,7 +3897,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3895,7 +3911,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3909,7 +3925,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3923,7 +3939,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -3937,7 +3953,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3957,11 +3973,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -3981,7 +3997,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3998,7 +4014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -4015,7 +4031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4032,7 +4048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4049,7 +4065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -4066,7 +4082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4083,7 +4099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -4100,7 +4116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4117,7 +4133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4134,7 +4150,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4151,7 +4167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -4168,7 +4184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4185,7 +4201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -4202,7 +4218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -4219,7 +4235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -4236,7 +4252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -4253,7 +4269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -4270,7 +4286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -4287,7 +4303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -4304,7 +4320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -4321,7 +4337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -4344,11 +4360,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -4407,7 +4423,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4463,7 +4479,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -4519,7 +4535,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4575,7 +4591,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4631,7 +4647,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -4693,11 +4709,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -4729,7 +4745,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4758,7 +4774,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -4787,7 +4803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4816,7 +4832,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4845,7 +4861,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -4874,7 +4890,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4903,7 +4919,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -4932,7 +4948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4961,7 +4977,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4990,7 +5006,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5025,11 +5041,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:BB22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:54">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -5193,7 +5209,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:54">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -5354,7 +5370,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:54">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -5515,7 +5531,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:54">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5676,7 +5692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:54">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -5837,7 +5853,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:54">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -5998,7 +6014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:54">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -6159,7 +6175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:54">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -6320,7 +6336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:54">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6481,7 +6497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:54">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6642,7 +6658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:54">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6803,7 +6819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:54">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -6964,7 +6980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:54">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -7125,7 +7141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:54">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -7286,7 +7302,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:54">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -7447,7 +7463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:54">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -7608,7 +7624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:53">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -7769,7 +7785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:53">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -7930,7 +7946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:53">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -8091,7 +8107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:53">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -8252,7 +8268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:53">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -8413,7 +8429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:53">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
